--- a/FASE 1/Planilha de Relacionamento Entrevista com Resultados Esperados.xlsx
+++ b/FASE 1/Planilha de Relacionamento Entrevista com Resultados Esperados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pucpredu-my.sharepoint.com/personal/stefany_oliveira_pucpr_edu_br/Documents/Documentos/GitHub/PROJETO-EXPERIENCIA-CRIATIVA-INOVANDO-EM-PROCESSOS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pucpredu-my.sharepoint.com/personal/stefany_oliveira_pucpr_edu_br/Documents/Documentos/GitHub/PROJETO-EXPERIENCIA-CRIATIVA-INOVANDO-EM-PROCESSOS/FASE 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43912C3D-0C3A-40BB-97E0-6F8E2457A8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{43912C3D-0C3A-40BB-97E0-6F8E2457A8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3695FE15-9129-4107-B213-6C329A44D10F}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{1FF8B5B1-1708-4B11-B968-C3D396F08296}"/>
+    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{1FF8B5B1-1708-4B11-B968-C3D396F08296}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="172">
   <si>
     <t>Processo</t>
   </si>
@@ -293,12 +293,6 @@
     <t>A empresa identifica e acompanha riscos ou oportunidades que possam afetar a organização como um todo? Se sim, como esses riscos ou oportunidades são analisados e comunicados?</t>
   </si>
   <si>
-    <t>Voces possuem indicadores ou métricas da empresa para acompanhar os objetivos organizacionais? Se sim, como esses dados são coletados e analisados pela gestão?</t>
-  </si>
-  <si>
-    <t>Como a empresa garante que os processos utilizados estejam alinhados com os objetivos estratégicos da organização? Esse alinhamento é revisado ou acompanhado pela gestão?</t>
-  </si>
-  <si>
     <t>PCP</t>
   </si>
   <si>
@@ -537,12 +531,6 @@
   </si>
   <si>
     <t>OSW5</t>
-  </si>
-  <si>
-    <t>OSW6</t>
-  </si>
-  <si>
-    <t>OSW7</t>
   </si>
   <si>
     <t>Quais indicadores ou métricas vocês utilizam para acompanhar o desempenho dos projetos ou processos da empresa? E como essas métricas são definidas?</t>
@@ -564,6 +552,9 @@
     <t xml:space="preserve">
 Gestor de Qualidade Organizacional
 </t>
+  </si>
+  <si>
+    <t>Gestor de Qualidade Organizacional</t>
   </si>
 </sst>
 </file>
@@ -613,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -636,14 +627,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -663,10 +648,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -986,17 +967,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDD2FFA-6174-4203-8360-9D23D3B908CE}">
-  <dimension ref="A1:D82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D80"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="4"/>
+    <col min="1" max="1" width="8.85546875" style="4"/>
     <col min="2" max="2" width="18" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.88671875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="23.109375" style="6" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="4"/>
+    <col min="3" max="3" width="61.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="6" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1010,1016 +991,992 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="9"/>
+      <c r="B3" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="9" t="s">
+      <c r="C4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="B5" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="9" t="s">
+      <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="9" t="s">
+      <c r="C6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="9" t="s">
+      <c r="C7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="9" t="s">
+      <c r="C8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="9" t="s">
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="9" t="s">
+      <c r="C10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="9" t="s">
+      <c r="C11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="9"/>
+      <c r="B12" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="9" t="s">
+      <c r="C12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="9" t="s">
+      <c r="C13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="9" t="s">
+      <c r="C14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="9"/>
+      <c r="B15" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="9" t="s">
-        <v>110</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="9" t="s">
+      <c r="D15" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="9"/>
+      <c r="B16" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="9"/>
+      <c r="B18" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="9" t="s">
+      <c r="C18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A19" s="9"/>
+      <c r="B19" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="9" t="s">
-        <v>114</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="D19" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="B20" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
+      <c r="D20" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="8" t="s">
+    <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="9"/>
+      <c r="B22" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="8" t="s">
+    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="9"/>
+      <c r="B23" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" s="8" t="s">
+    <row r="24" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+      <c r="B24" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="8" t="s">
+    <row r="25" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+      <c r="B25" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>75</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="C26" s="8" t="s">
+    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="9"/>
+      <c r="B26" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>30</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
+    <row r="27" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="B28" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="9"/>
+      <c r="B29" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="9"/>
+      <c r="B31" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="9"/>
+      <c r="B32" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="9"/>
+      <c r="B33" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="B34" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
+      <c r="B35" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="B36" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="9"/>
+      <c r="B37" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
+      <c r="B38" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="9"/>
+      <c r="B39" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A40" s="9"/>
+      <c r="B40" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="9"/>
+      <c r="B42" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="9"/>
+      <c r="B43" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="9"/>
+      <c r="B44" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="9"/>
+      <c r="B45" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="9"/>
+      <c r="B46" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="9"/>
+      <c r="B47" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="9"/>
+      <c r="B48" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="9"/>
+      <c r="B50" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="9"/>
+      <c r="B51" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="9"/>
+      <c r="B52" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="9"/>
+      <c r="B53" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="9"/>
+      <c r="B54" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="9"/>
+      <c r="B55" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56" s="9"/>
+      <c r="B56" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D57" s="8" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="6" t="s">
+    <row r="58" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A58" s="9"/>
+      <c r="B58" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="8" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" s="6" t="s">
+    <row r="59" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A59" s="9"/>
+      <c r="B59" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" s="8" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" s="6" t="s">
+    <row r="60" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A60" s="9"/>
+      <c r="B60" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A61" s="9"/>
+      <c r="B61" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A62" s="9"/>
+      <c r="B62" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A63" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A64" s="9"/>
+      <c r="B64" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="9"/>
+      <c r="B65" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="9"/>
+      <c r="B66" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A67" s="9"/>
+      <c r="B67" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="9"/>
+      <c r="B68" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A69" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A70" s="9"/>
+      <c r="B70" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A71" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A72" s="9"/>
+      <c r="B72" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A73" s="9"/>
+      <c r="B73" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A74" s="9"/>
+      <c r="B74" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A75" s="9"/>
+      <c r="B75" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A76" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D76" s="8" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" s="6" t="s">
+    <row r="77" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A77" s="9"/>
+      <c r="B77" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D77" s="8" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D32" s="6" t="s">
+    <row r="78" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A78" s="9"/>
+      <c r="B78" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D78" s="8" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D33" s="6" t="s">
+    <row r="79" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A79" s="9"/>
+      <c r="B79" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D79" s="8" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="11"/>
-      <c r="B34" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="11"/>
-      <c r="B35" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="11"/>
-      <c r="B38" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="11"/>
-      <c r="B39" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="11"/>
-      <c r="B42" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="11"/>
-      <c r="B43" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="11"/>
-      <c r="B45" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="11"/>
-      <c r="B46" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="11"/>
-      <c r="B47" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
-      <c r="B48" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
-      <c r="B51" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="11"/>
-      <c r="B53" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
-      <c r="B54" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="11"/>
-      <c r="B58" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="11"/>
-      <c r="B59" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="11"/>
-      <c r="B60" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="11"/>
-      <c r="B61" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="11"/>
-      <c r="B62" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="11"/>
-      <c r="B64" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
-      <c r="B65" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="11"/>
-      <c r="B66" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="11"/>
-      <c r="B67" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="11"/>
-      <c r="B68" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="11"/>
-      <c r="B70" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A71" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="11"/>
-      <c r="B72" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="11"/>
-      <c r="B73" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="11"/>
-      <c r="B74" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="11"/>
-      <c r="B75" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="11"/>
-      <c r="B77" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A78" s="11"/>
-      <c r="B78" s="9" t="s">
+    <row r="80" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A80" s="9"/>
+      <c r="B80" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="C78" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A79" s="11"/>
-      <c r="B79" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="11"/>
-      <c r="B80" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="C80" s="8" t="s">
+      <c r="C80" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D80" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A81" s="11"/>
-      <c r="B81" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A82" s="11"/>
-      <c r="B82" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D82" s="6" t="s">
+      <c r="D80" s="8" t="s">
         <v>171</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:A20"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="A36:A40"/>
     <mergeCell ref="A71:A75"/>
-    <mergeCell ref="A76:A82"/>
+    <mergeCell ref="A76:A80"/>
     <mergeCell ref="A41:A48"/>
     <mergeCell ref="A49:A56"/>
     <mergeCell ref="A57:A62"/>
     <mergeCell ref="A63:A68"/>
     <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A2:A20"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="A36:A40"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/FASE 1/Planilha de Relacionamento Entrevista com Resultados Esperados.xlsx
+++ b/FASE 1/Planilha de Relacionamento Entrevista com Resultados Esperados.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="5" documentId="8_{43912C3D-0C3A-40BB-97E0-6F8E2457A8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3695FE15-9129-4107-B213-6C329A44D10F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{1FF8B5B1-1708-4B11-B968-C3D396F08296}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1FF8B5B1-1708-4B11-B968-C3D396F08296}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -1965,11 +1965,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A2:A20"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="A36:A40"/>
     <mergeCell ref="A71:A75"/>
     <mergeCell ref="A76:A80"/>
     <mergeCell ref="A41:A48"/>
@@ -1977,6 +1972,11 @@
     <mergeCell ref="A57:A62"/>
     <mergeCell ref="A63:A68"/>
     <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A2:A20"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="A36:A40"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
